--- a/data/Limpia/Ubicaciones_direcciones.xlsx
+++ b/data/Limpia/Ubicaciones_direcciones.xlsx
@@ -438,7 +438,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CODIGO</t>
+          <t>CODCLI2</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -511,7 +511,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81227</v>
+        <v>81125</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>11548</v>
+        <v>82210</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>22358</v>
+        <v>22360</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>82206</v>
+        <v>80297</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>80305</v>
+        <v>82157</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>62905</v>
+        <v>62950</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>81227</v>
+        <v>81125</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>62990</v>
+        <v>62970</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>80136</v>
+        <v>22124</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>82003</v>
+        <v>13006</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>12908</v>
+        <v>55555</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>80009</v>
+        <v>21920</v>
       </c>
       <c r="B387" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>80001</v>
+        <v>80209</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>81101</v>
+        <v>41971</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
@@ -14516,7 +14516,7 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>13030</v>
+        <v>81136</v>
       </c>
       <c r="B428" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>80005</v>
+        <v>80303</v>
       </c>
       <c r="B444" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>22923</v>
+        <v>80189</v>
       </c>
       <c r="B460" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>81001</v>
+        <v>62783</v>
       </c>
       <c r="B499" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>62915</v>
+        <v>63010</v>
       </c>
       <c r="B503" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>62780</v>
+        <v>63000</v>
       </c>
       <c r="B506" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>13035</v>
+        <v>81113</v>
       </c>
       <c r="B509" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>11897</v>
+        <v>82107</v>
       </c>
       <c r="B530" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
     </row>
     <row r="577">
       <c r="A577" t="n">
-        <v>12888</v>
+        <v>82185</v>
       </c>
       <c r="B577" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
     </row>
     <row r="578">
       <c r="A578" t="n">
-        <v>12932</v>
+        <v>13330</v>
       </c>
       <c r="B578" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>12145</v>
+        <v>13200</v>
       </c>
       <c r="B600" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
     </row>
     <row r="606">
       <c r="A606" t="n">
-        <v>11889</v>
+        <v>81124</v>
       </c>
       <c r="B606" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
     </row>
     <row r="613">
       <c r="A613" t="n">
-        <v>11979</v>
+        <v>11891</v>
       </c>
       <c r="B613" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
     </row>
     <row r="616">
       <c r="A616" t="n">
-        <v>12923</v>
+        <v>42940</v>
       </c>
       <c r="B616" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
     </row>
     <row r="619">
       <c r="A619" t="n">
-        <v>62665</v>
+        <v>62998</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>62900</v>
+        <v>62611</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>22338</v>
+        <v>23200</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
@@ -21429,7 +21429,7 @@
     </row>
     <row r="644">
       <c r="A644" t="n">
-        <v>41950</v>
+        <v>123344</v>
       </c>
       <c r="B644" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
     </row>
     <row r="649">
       <c r="A649" t="n">
-        <v>41905</v>
+        <v>82157</v>
       </c>
       <c r="B649" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
     </row>
     <row r="656">
       <c r="A656" t="n">
-        <v>13080</v>
+        <v>81129</v>
       </c>
       <c r="B656" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
     </row>
     <row r="657">
       <c r="A657" t="n">
-        <v>13095</v>
+        <v>12918</v>
       </c>
       <c r="B657" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
     </row>
     <row r="702">
       <c r="A702" t="n">
-        <v>22044</v>
+        <v>23305</v>
       </c>
       <c r="B702" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
     </row>
     <row r="726">
       <c r="A726" t="n">
-        <v>11984</v>
+        <v>81237</v>
       </c>
       <c r="B726" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
     </row>
     <row r="727">
       <c r="A727" t="n">
-        <v>11879</v>
+        <v>11891</v>
       </c>
       <c r="B727" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
     </row>
     <row r="735">
       <c r="A735" t="n">
-        <v>42925</v>
+        <v>42945</v>
       </c>
       <c r="B735" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CODIGO</t>
+          <t>CODCLI2</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -24761,7 +24761,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45975.59782020297</v>
+        <v>45980.39141747875</v>
       </c>
     </row>
     <row r="3">
